--- a/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536322_LIGAREGULARB_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536322_LIGAREGULARB_PROCESSED.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y24"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1704,7 +1704,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. YAÑEZ GAMBIN</t>
+          <t>D. YANEZ GAMBIN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1716,40 +1716,40 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5918</v>
+        <v>-0.6465</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5918</v>
+        <v>-0.6312</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>-0.0153</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5918</v>
+        <v>-0.6148</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>-0.4257</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5918</v>
+        <v>-0.189</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5918</v>
+        <v>-0.7879</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>-0.7096</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5918</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>0.1731</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>0.2838</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>-0.1107</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -1761,13 +1761,13 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-0.0318</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>0.1567</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>-0.1885</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1787,7 +1787,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. YANEZ GAMBIN</t>
+          <t>C. TOLEDO ZAMORA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1799,58 +1799,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.2383</v>
+        <v>-2.0435</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.223</v>
+        <v>-1.4151</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0153</v>
+        <v>-0.6284999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.2065</v>
+        <v>-2.2405</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4257</v>
+        <v>-1.68</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7808</v>
+        <v>-0.5606</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.3797</v>
+        <v>-1.183</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.7096</v>
+        <v>-1.3802</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6701</v>
+        <v>0.1973</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1731</v>
+        <v>-1.0575</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2838</v>
+        <v>-0.2997</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1107</v>
+        <v>-0.7578</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.2055</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.2055</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0318</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1567</v>
+        <v>-0.2321</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1885</v>
+        <v>0.2236</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1870,7 +1870,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. TOLEDO ZAMORA</t>
+          <t>K. SOW</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1882,67 +1882,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.0435</v>
+        <v>-3.6779</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.4151</v>
+        <v>-0.1284</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6284999999999999</v>
+        <v>-3.5495</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.2405</v>
+        <v>-2.5523</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.68</v>
+        <v>-1.8652</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5606</v>
+        <v>-0.6871</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.183</v>
+        <v>0.1096</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.3802</v>
+        <v>-0.7189</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1973</v>
+        <v>0.8285</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0575</v>
+        <v>-2.662</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2997</v>
+        <v>-1.1463</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.7578</v>
+        <v>-1.5156</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2055</v>
+        <v>0.411</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2055</v>
+        <v>0.411</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.3585</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2321</v>
+        <v>-0.238</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2236</v>
+        <v>-0.1204</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-1.1781</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.1781</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. SOW</t>
+          <t>J. MARTINEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1965,67 +1965,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.6779</v>
+        <v>-3.9825</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1284</v>
+        <v>-0.185</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.5495</v>
+        <v>-3.7975</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.5523</v>
+        <v>0.1427</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.8652</v>
+        <v>-0.3466</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6871</v>
+        <v>0.4893</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1096</v>
+        <v>1.9526</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.7189</v>
+        <v>0.0584</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8285</v>
+        <v>1.8943</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.662</v>
+        <v>-1.8099</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1463</v>
+        <v>-0.4049</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.5156</v>
+        <v>-1.4049</v>
       </c>
       <c r="P19" t="n">
-        <v>0.411</v>
+        <v>-1.6439</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.0548</v>
       </c>
       <c r="R19" t="n">
         <v>0.411</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3585</v>
+        <v>-0.4745</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.238</v>
+        <v>-0.0828</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1204</v>
+        <v>-0.3917</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.1781</v>
+        <v>-2.0068</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.1781</v>
+        <v>-2.0068</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. MARTINEZ SANCHEZ</t>
+          <t>I. ALVAREZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2048,67 +2048,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.9825</v>
+        <v>-4.0152</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.185</v>
+        <v>-1.343</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.7975</v>
+        <v>-2.6723</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1427</v>
+        <v>0.8126</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3466</v>
+        <v>-0.2608</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4893</v>
+        <v>1.0734</v>
       </c>
       <c r="J20" t="n">
-        <v>1.9526</v>
+        <v>2.6231</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0584</v>
+        <v>0.8855</v>
       </c>
       <c r="L20" t="n">
-        <v>1.8943</v>
+        <v>1.7376</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.8099</v>
+        <v>-1.8105</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4049</v>
+        <v>-1.1463</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.4049</v>
+        <v>-0.6642</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.6439</v>
+        <v>-3.2877</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.0548</v>
+        <v>-4.1096</v>
       </c>
       <c r="R20" t="n">
-        <v>0.411</v>
+        <v>0.8219</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4745</v>
+        <v>-0.1223</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0828</v>
+        <v>-0.0961</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3917</v>
+        <v>-0.0262</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.0068</v>
+        <v>-1.4178</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2397</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.0068</v>
+        <v>-1.6575</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. ALVAREZ FERNANDEZ</t>
+          <t>G. GIL GARCIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2131,67 +2131,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.0152</v>
+        <v>-5.3099</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.343</v>
+        <v>0.4743</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.6723</v>
+        <v>-5.7842</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8126</v>
+        <v>-4.9295</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2608</v>
+        <v>-3.5805</v>
       </c>
       <c r="I21" t="n">
-        <v>1.0734</v>
+        <v>-1.349</v>
       </c>
       <c r="J21" t="n">
-        <v>2.6231</v>
+        <v>0.2985</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8855</v>
+        <v>0.7307</v>
       </c>
       <c r="L21" t="n">
-        <v>1.7376</v>
+        <v>-0.4323</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.8105</v>
+        <v>-5.228</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1463</v>
+        <v>-4.3112</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6642</v>
+        <v>-0.9167999999999999</v>
       </c>
       <c r="P21" t="n">
-        <v>-3.2877</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.1096</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.8219</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1223</v>
+        <v>0.4209</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0961</v>
+        <v>0.1758</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0262</v>
+        <v>0.2451</v>
       </c>
       <c r="V21" t="n">
         <v>-1.4178</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2397</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.6575</v>
+        <v>-1.4178</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. GIL GARCIA</t>
+          <t>J. MILLER</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2214,67 +2214,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.3099</v>
+        <v>-5.7546</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4743</v>
+        <v>-0.1432</v>
       </c>
       <c r="F22" t="n">
-        <v>-5.7842</v>
+        <v>-5.6114</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.9295</v>
+        <v>-5.387</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.5805</v>
+        <v>-3.4545</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.349</v>
+        <v>-1.9326</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2985</v>
+        <v>1.0557</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7307</v>
+        <v>0.8567</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.4323</v>
+        <v>0.199</v>
       </c>
       <c r="M22" t="n">
-        <v>-5.228</v>
+        <v>-6.4428</v>
       </c>
       <c r="N22" t="n">
         <v>-4.3112</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9167999999999999</v>
+        <v>-2.1315</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6163999999999999</v>
+        <v>-0.6163999999999999</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.0274</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6163999999999999</v>
+        <v>0.411</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4209</v>
+        <v>-0.4498</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1758</v>
+        <v>-0.1716</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2451</v>
+        <v>-0.2782</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.4178</v>
+        <v>0.6986</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.4178</v>
+        <v>0.6986</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. MILLER</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2297,152 +2297,69 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.7546</v>
+        <v>-18.7899</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1432</v>
+        <v>15.9954</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.6114</v>
+        <v>-34.7854</v>
       </c>
       <c r="G23" t="n">
-        <v>-5.387</v>
+        <v>-8.382899999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.4545</v>
+        <v>-18.6433</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.9326</v>
+        <v>10.2603</v>
       </c>
       <c r="J23" t="n">
-        <v>1.0557</v>
+        <v>25.8337</v>
       </c>
       <c r="K23" t="n">
-        <v>0.8567</v>
+        <v>3.964800000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>0.199</v>
+        <v>21.869</v>
       </c>
       <c r="M23" t="n">
-        <v>-6.4428</v>
+        <v>-34.2169</v>
       </c>
       <c r="N23" t="n">
-        <v>-4.3112</v>
+        <v>-22.6081</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.1315</v>
+        <v>-11.6085</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.6163999999999999</v>
+        <v>-9.246699999999999</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.0274</v>
+        <v>-14.3836</v>
       </c>
       <c r="R23" t="n">
-        <v>0.411</v>
+        <v>5.136999999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4498</v>
+        <v>0.1476999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1716</v>
+        <v>-0.7766</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2782</v>
+        <v>0.9244000000000001</v>
       </c>
       <c r="V23" t="n">
-        <v>0.6986</v>
+        <v>-1.308299999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>5.3219</v>
       </c>
       <c r="X23" t="n">
-        <v>0.6986</v>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>play_by_play_2536322_LIGAREGULARB_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>LA SALUD CARTAGENA C.B.</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" t="n">
-        <v>-18.7899</v>
-      </c>
-      <c r="E24" t="n">
-        <v>15.9954</v>
-      </c>
-      <c r="F24" t="n">
-        <v>-34.7854</v>
-      </c>
-      <c r="G24" t="n">
-        <v>-8.3828</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-18.6433</v>
-      </c>
-      <c r="I24" t="n">
-        <v>10.2603</v>
-      </c>
-      <c r="J24" t="n">
-        <v>25.8337</v>
-      </c>
-      <c r="K24" t="n">
-        <v>3.9648</v>
-      </c>
-      <c r="L24" t="n">
-        <v>21.869</v>
-      </c>
-      <c r="M24" t="n">
-        <v>-34.2169</v>
-      </c>
-      <c r="N24" t="n">
-        <v>-22.6081</v>
-      </c>
-      <c r="O24" t="n">
-        <v>-11.6085</v>
-      </c>
-      <c r="P24" t="n">
-        <v>-9.246700000000001</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>-14.3836</v>
-      </c>
-      <c r="R24" t="n">
-        <v>5.136999999999999</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0.1476999999999999</v>
-      </c>
-      <c r="T24" t="n">
-        <v>-0.7766</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0.9244000000000001</v>
-      </c>
-      <c r="V24" t="n">
-        <v>-1.3083</v>
-      </c>
-      <c r="W24" t="n">
-        <v>5.3219</v>
-      </c>
-      <c r="X24" t="n">
         <v>-6.6301</v>
       </c>
-      <c r="Y24" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
